--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Puchar Lata 2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SZABLON (Biegi)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Puchar Lata 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SZABLON (Biegi)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,27 @@
       <name val="Segoe UI"/>
       <color rgb="00595959"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -141,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,6 +207,42 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:P45"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -573,6 +630,7 @@
     <col width="8" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -587,6 +645,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -815,41 +874,32 @@
           <t>Suma punktów</t>
         </is>
       </c>
-      <c r="C11" s="9">
-        <f>SUM(C6:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>SUM(D6:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="9">
-        <f>SUM(E6:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="9">
-        <f>SUM(F6:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="9">
-        <f>SUM(G6:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="9">
-        <f>SUM(H6:H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="9">
-        <f>SUM(I6:I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="9">
-        <f>SUM(J6:J10)</f>
-        <v/>
-      </c>
-      <c r="K11" s="9">
-        <f>SUM(K6:K10)</f>
-        <v/>
+      <c r="C11" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -858,41 +908,32 @@
           <t>Średnia na bieg</t>
         </is>
       </c>
-      <c r="C12" s="10">
-        <f>AVERAGE(C6:C10)</f>
-        <v/>
-      </c>
-      <c r="D12" s="10">
-        <f>AVERAGE(D6:D10)</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>AVERAGE(E6:E10)</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>AVERAGE(F6:F10)</f>
-        <v/>
-      </c>
-      <c r="G12" s="10">
-        <f>AVERAGE(G6:G10)</f>
-        <v/>
-      </c>
-      <c r="H12" s="10">
-        <f>AVERAGE(H6:H10)</f>
-        <v/>
-      </c>
-      <c r="I12" s="10">
-        <f>AVERAGE(I6:I10)</f>
-        <v/>
-      </c>
-      <c r="J12" s="10">
-        <f>AVERAGE(J6:J10)</f>
-        <v/>
-      </c>
-      <c r="K12" s="10">
-        <f>AVERAGE(K6:K10)</f>
-        <v/>
+      <c r="C12" s="18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -935,43 +976,35 @@
           <t>Punkty Turniejowe</t>
         </is>
       </c>
-      <c r="C14" s="14">
-        <f>CHOOSE(C13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>CHOOSE(D13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>CHOOSE(E13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="14">
-        <f>CHOOSE(F13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>CHOOSE(G13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="14">
-        <f>CHOOSE(H13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="14">
-        <f>CHOOSE(I13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="14">
-        <f>CHOOSE(J13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="K14" s="14">
-        <f>CHOOSE(K13,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="C14" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -1247,49 +1280,38 @@
           <t>Suma punktów</t>
         </is>
       </c>
-      <c r="C23" s="9">
-        <f>SUM(C18:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="9">
-        <f>SUM(D18:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="9">
-        <f>SUM(E18:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="9">
-        <f>SUM(F18:F22)</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>SUM(G18:G22)</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>SUM(H18:H22)</f>
-        <v/>
-      </c>
-      <c r="I23" s="9">
-        <f>SUM(I18:I22)</f>
-        <v/>
-      </c>
-      <c r="J23" s="9">
-        <f>SUM(J18:J22)</f>
-        <v/>
-      </c>
-      <c r="K23" s="9">
-        <f>SUM(K18:K22)</f>
-        <v/>
-      </c>
-      <c r="L23" s="9">
-        <f>SUM(L18:L22)</f>
-        <v/>
-      </c>
-      <c r="M23" s="9">
-        <f>SUM(M18:M22)</f>
-        <v/>
+      <c r="C23" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="24">
@@ -1298,49 +1320,38 @@
           <t>Średnia na bieg</t>
         </is>
       </c>
-      <c r="C24" s="10">
-        <f>AVERAGE(C18:C22)</f>
-        <v/>
-      </c>
-      <c r="D24" s="10">
-        <f>AVERAGE(D18:D22)</f>
-        <v/>
-      </c>
-      <c r="E24" s="10">
-        <f>AVERAGE(E18:E22)</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>AVERAGE(F18:F22)</f>
-        <v/>
-      </c>
-      <c r="G24" s="10">
-        <f>AVERAGE(G18:G22)</f>
-        <v/>
-      </c>
-      <c r="H24" s="10">
-        <f>AVERAGE(H18:H22)</f>
-        <v/>
-      </c>
-      <c r="I24" s="10">
-        <f>AVERAGE(I18:I22)</f>
-        <v/>
-      </c>
-      <c r="J24" s="10">
-        <f>AVERAGE(J18:J22)</f>
-        <v/>
-      </c>
-      <c r="K24" s="10">
-        <f>AVERAGE(K18:K22)</f>
-        <v/>
-      </c>
-      <c r="L24" s="10">
-        <f>AVERAGE(L18:L22)</f>
-        <v/>
-      </c>
-      <c r="M24" s="10">
-        <f>AVERAGE(M18:M22)</f>
-        <v/>
+      <c r="C24" s="18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="25">
@@ -1389,584 +1400,1595 @@
           <t>Punkty Turniejowe</t>
         </is>
       </c>
-      <c r="C26" s="14">
-        <f>CHOOSE(C25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="D26" s="14">
-        <f>CHOOSE(D25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="E26" s="14">
-        <f>CHOOSE(E25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="F26" s="14">
-        <f>CHOOSE(F25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="14">
-        <f>CHOOSE(G25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="H26" s="14">
-        <f>CHOOSE(H25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="14">
-        <f>CHOOSE(I25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="14">
-        <f>CHOOSE(J25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="K26" s="14">
-        <f>CHOOSE(K25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="L26" s="14">
-        <f>CHOOSE(L25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
-      </c>
-      <c r="M26" s="14">
-        <f>CHOOSE(M25,20,18,16,14,12,10,9,8,7,6,5,4,3,2,1,0,0)</f>
-        <v/>
+      <c r="C26" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Runda III • Piątek, 24.07.2026</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F36" s="24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G36" s="24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H36" s="24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J36" s="24" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
+      <c r="O42" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P30" s="3" t="inlineStr">
+      <c r="P42" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="6">
-        <f>RANK(P31, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="27" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="E43" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O43" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="G44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P44" s="17" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>DAN</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D45" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="E31" s="15" t="n">
+      <c r="E45" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="F31" s="15" t="inlineStr"/>
-      <c r="G31" s="15" t="inlineStr"/>
-      <c r="H31" s="15" t="inlineStr"/>
-      <c r="I31" s="15" t="inlineStr"/>
-      <c r="J31" s="15" t="inlineStr"/>
-      <c r="K31" s="15" t="inlineStr"/>
-      <c r="L31" s="15" t="inlineStr"/>
-      <c r="M31" s="15" t="inlineStr"/>
-      <c r="N31" s="15" t="inlineStr"/>
-      <c r="O31" s="15" t="inlineStr"/>
-      <c r="P31" s="9">
-        <f>SUM(D31:O31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="4">
-        <f>RANK(P32, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="n">
+      <c r="F45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="G46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="27" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="G47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P47" s="17" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="F48" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P48" s="17" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E49" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D50" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="17" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" s="27" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="G51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="17" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D52" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P52" s="17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C53" s="27" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F53" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O53" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P53" s="17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O54" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="C55" s="27" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P55" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="F32" s="16" t="inlineStr"/>
-      <c r="G32" s="16" t="inlineStr"/>
-      <c r="H32" s="16" t="inlineStr"/>
-      <c r="I32" s="16" t="inlineStr"/>
-      <c r="J32" s="16" t="inlineStr"/>
-      <c r="K32" s="16" t="inlineStr"/>
-      <c r="L32" s="16" t="inlineStr"/>
-      <c r="M32" s="16" t="inlineStr"/>
-      <c r="N32" s="16" t="inlineStr"/>
-      <c r="O32" s="16" t="inlineStr"/>
-      <c r="P32" s="9">
-        <f>SUM(D32:O32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6">
-        <f>RANK(P33, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E33" s="15" t="n">
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O56" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P57" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="29" t="n">
         <v>16</v>
       </c>
-      <c r="F33" s="15" t="inlineStr"/>
-      <c r="G33" s="15" t="inlineStr"/>
-      <c r="H33" s="15" t="inlineStr"/>
-      <c r="I33" s="15" t="inlineStr"/>
-      <c r="J33" s="15" t="inlineStr"/>
-      <c r="K33" s="15" t="inlineStr"/>
-      <c r="L33" s="15" t="inlineStr"/>
-      <c r="M33" s="15" t="inlineStr"/>
-      <c r="N33" s="15" t="inlineStr"/>
-      <c r="O33" s="15" t="inlineStr"/>
-      <c r="P33" s="9">
-        <f>SUM(D33:O33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="4">
-        <f>RANK(P34, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="16" t="inlineStr"/>
-      <c r="H34" s="16" t="inlineStr"/>
-      <c r="I34" s="16" t="inlineStr"/>
-      <c r="J34" s="16" t="inlineStr"/>
-      <c r="K34" s="16" t="inlineStr"/>
-      <c r="L34" s="16" t="inlineStr"/>
-      <c r="M34" s="16" t="inlineStr"/>
-      <c r="N34" s="16" t="inlineStr"/>
-      <c r="O34" s="16" t="inlineStr"/>
-      <c r="P34" s="9">
-        <f>SUM(D34:O34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6">
-        <f>RANK(P35, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="F35" s="15" t="inlineStr"/>
-      <c r="G35" s="15" t="inlineStr"/>
-      <c r="H35" s="15" t="inlineStr"/>
-      <c r="I35" s="15" t="inlineStr"/>
-      <c r="J35" s="15" t="inlineStr"/>
-      <c r="K35" s="15" t="inlineStr"/>
-      <c r="L35" s="15" t="inlineStr"/>
-      <c r="M35" s="15" t="inlineStr"/>
-      <c r="N35" s="15" t="inlineStr"/>
-      <c r="O35" s="15" t="inlineStr"/>
-      <c r="P35" s="9">
-        <f>SUM(D35:O35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="4">
-        <f>RANK(P36, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="F36" s="16" t="inlineStr"/>
-      <c r="G36" s="16" t="inlineStr"/>
-      <c r="H36" s="16" t="inlineStr"/>
-      <c r="I36" s="16" t="inlineStr"/>
-      <c r="J36" s="16" t="inlineStr"/>
-      <c r="K36" s="16" t="inlineStr"/>
-      <c r="L36" s="16" t="inlineStr"/>
-      <c r="M36" s="16" t="inlineStr"/>
-      <c r="N36" s="16" t="inlineStr"/>
-      <c r="O36" s="16" t="inlineStr"/>
-      <c r="P36" s="9">
-        <f>SUM(D36:O36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="6">
-        <f>RANK(P37, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F37" s="15" t="inlineStr"/>
-      <c r="G37" s="15" t="inlineStr"/>
-      <c r="H37" s="15" t="inlineStr"/>
-      <c r="I37" s="15" t="inlineStr"/>
-      <c r="J37" s="15" t="inlineStr"/>
-      <c r="K37" s="15" t="inlineStr"/>
-      <c r="L37" s="15" t="inlineStr"/>
-      <c r="M37" s="15" t="inlineStr"/>
-      <c r="N37" s="15" t="inlineStr"/>
-      <c r="O37" s="15" t="inlineStr"/>
-      <c r="P37" s="9">
-        <f>SUM(D37:O37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="4">
-        <f>RANK(P38, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F38" s="16" t="inlineStr"/>
-      <c r="G38" s="16" t="inlineStr"/>
-      <c r="H38" s="16" t="inlineStr"/>
-      <c r="I38" s="16" t="inlineStr"/>
-      <c r="J38" s="16" t="inlineStr"/>
-      <c r="K38" s="16" t="inlineStr"/>
-      <c r="L38" s="16" t="inlineStr"/>
-      <c r="M38" s="16" t="inlineStr"/>
-      <c r="N38" s="16" t="inlineStr"/>
-      <c r="O38" s="16" t="inlineStr"/>
-      <c r="P38" s="9">
-        <f>SUM(D38:O38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="6">
-        <f>RANK(P39, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="15" t="inlineStr"/>
-      <c r="G39" s="15" t="inlineStr"/>
-      <c r="H39" s="15" t="inlineStr"/>
-      <c r="I39" s="15" t="inlineStr"/>
-      <c r="J39" s="15" t="inlineStr"/>
-      <c r="K39" s="15" t="inlineStr"/>
-      <c r="L39" s="15" t="inlineStr"/>
-      <c r="M39" s="15" t="inlineStr"/>
-      <c r="N39" s="15" t="inlineStr"/>
-      <c r="O39" s="15" t="inlineStr"/>
-      <c r="P39" s="9">
-        <f>SUM(D39:O39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="4">
-        <f>RANK(P40, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>DOM</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr"/>
-      <c r="G40" s="16" t="inlineStr"/>
-      <c r="H40" s="16" t="inlineStr"/>
-      <c r="I40" s="16" t="inlineStr"/>
-      <c r="J40" s="16" t="inlineStr"/>
-      <c r="K40" s="16" t="inlineStr"/>
-      <c r="L40" s="16" t="inlineStr"/>
-      <c r="M40" s="16" t="inlineStr"/>
-      <c r="N40" s="16" t="inlineStr"/>
-      <c r="O40" s="16" t="inlineStr"/>
-      <c r="P40" s="9">
-        <f>SUM(D40:O40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="6">
-        <f>RANK(P41, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="15" t="inlineStr"/>
-      <c r="G41" s="15" t="inlineStr"/>
-      <c r="H41" s="15" t="inlineStr"/>
-      <c r="I41" s="15" t="inlineStr"/>
-      <c r="J41" s="15" t="inlineStr"/>
-      <c r="K41" s="15" t="inlineStr"/>
-      <c r="L41" s="15" t="inlineStr"/>
-      <c r="M41" s="15" t="inlineStr"/>
-      <c r="N41" s="15" t="inlineStr"/>
-      <c r="O41" s="15" t="inlineStr"/>
-      <c r="P41" s="9">
-        <f>SUM(D41:O41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="4">
-        <f>RANK(P42, $P$31:$P$45)</f>
-        <v/>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F42" s="16" t="inlineStr"/>
-      <c r="G42" s="16" t="inlineStr"/>
-      <c r="H42" s="16" t="inlineStr"/>
-      <c r="I42" s="16" t="inlineStr"/>
-      <c r="J42" s="16" t="inlineStr"/>
-      <c r="K42" s="16" t="inlineStr"/>
-      <c r="L42" s="16" t="inlineStr"/>
-      <c r="M42" s="16" t="inlineStr"/>
-      <c r="N42" s="16" t="inlineStr"/>
-      <c r="O42" s="16" t="inlineStr"/>
-      <c r="P42" s="9">
-        <f>SUM(D42:O42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="6">
-        <f>IF(C43="","",RANK(P43, $P$31:$P$45))</f>
-        <v/>
-      </c>
-      <c r="C43" s="6" t="inlineStr"/>
-      <c r="D43" s="15" t="inlineStr"/>
-      <c r="E43" s="15" t="inlineStr"/>
-      <c r="F43" s="15" t="inlineStr"/>
-      <c r="G43" s="15" t="inlineStr"/>
-      <c r="H43" s="15" t="inlineStr"/>
-      <c r="I43" s="15" t="inlineStr"/>
-      <c r="J43" s="15" t="inlineStr"/>
-      <c r="K43" s="15" t="inlineStr"/>
-      <c r="L43" s="15" t="inlineStr"/>
-      <c r="M43" s="15" t="inlineStr"/>
-      <c r="N43" s="15" t="inlineStr"/>
-      <c r="O43" s="15" t="inlineStr"/>
-      <c r="P43" s="9">
-        <f>IF(C43="","",SUM(D43:O43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="4">
-        <f>IF(C44="","",RANK(P44, $P$31:$P$45))</f>
-        <v/>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="16" t="inlineStr"/>
-      <c r="E44" s="16" t="inlineStr"/>
-      <c r="F44" s="16" t="inlineStr"/>
-      <c r="G44" s="16" t="inlineStr"/>
-      <c r="H44" s="16" t="inlineStr"/>
-      <c r="I44" s="16" t="inlineStr"/>
-      <c r="J44" s="16" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
-      <c r="M44" s="16" t="inlineStr"/>
-      <c r="N44" s="16" t="inlineStr"/>
-      <c r="O44" s="16" t="inlineStr"/>
-      <c r="P44" s="9">
-        <f>IF(C44="","",SUM(D44:O44))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="6">
-        <f>IF(C45="","",RANK(P45, $P$31:$P$45))</f>
-        <v/>
-      </c>
-      <c r="C45" s="6" t="inlineStr"/>
-      <c r="D45" s="15" t="inlineStr"/>
-      <c r="E45" s="15" t="inlineStr"/>
-      <c r="F45" s="15" t="inlineStr"/>
-      <c r="G45" s="15" t="inlineStr"/>
-      <c r="H45" s="15" t="inlineStr"/>
-      <c r="I45" s="15" t="inlineStr"/>
-      <c r="J45" s="15" t="inlineStr"/>
-      <c r="K45" s="15" t="inlineStr"/>
-      <c r="L45" s="15" t="inlineStr"/>
-      <c r="M45" s="15" t="inlineStr"/>
-      <c r="N45" s="15" t="inlineStr"/>
-      <c r="O45" s="15" t="inlineStr"/>
-      <c r="P45" s="9">
-        <f>IF(C45="","",SUM(D45:O45))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P58" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S81"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1769,939 +1769,509 @@
       </c>
     </row>
     <row r="39"/>
-    <row r="40"/>
+    <row r="40">
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>Runda IV • Piątek, 31.07.2026</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="L42" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" s="22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H46" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="J47" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K47" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D48" s="24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E48" s="24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F48" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" s="24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H48" s="24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J48" s="24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L48" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N42" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
+      <c r="O54" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr">
+      <c r="P54" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D43" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="E43" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F43" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O43" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="17" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C44" s="29" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D44" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="E44" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="F44" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="G44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O44" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P44" s="17" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D45" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="E45" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="F45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O45" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P45" s="17" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" s="29" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D46" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="E46" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="F46" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="G46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P46" s="17" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="G47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O47" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P47" s="17" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="C48" s="29" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="F48" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O48" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P48" s="17" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D49" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="E49" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="F49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O49" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="17" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="C50" s="29" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="E50" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="F50" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O50" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P50" s="17" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>KAL</t>
-        </is>
-      </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="G51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="17" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="C52" s="29" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E52" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O52" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P52" s="17" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="C53" s="27" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="F53" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="G53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O53" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P53" s="17" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="C54" s="29" t="inlineStr">
-        <is>
-          <t>DOM</t>
-        </is>
-      </c>
-      <c r="D54" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="E54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O54" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P54" s="17" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="27" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>18</v>
       </c>
       <c r="E55" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="F55" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="G55" s="28" t="n">
+        <v>20</v>
       </c>
       <c r="H55" s="28" t="inlineStr">
         <is>
@@ -2744,37 +2314,29 @@
         </is>
       </c>
       <c r="P55" s="17" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="29" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="D56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="E56" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="F56" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="G56" s="30" t="n">
+        <v>16</v>
       </c>
       <c r="H56" s="30" t="inlineStr">
         <is>
@@ -2817,37 +2379,29 @@
         </is>
       </c>
       <c r="P56" s="17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>TAS</t>
-        </is>
-      </c>
-      <c r="D57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E57" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="28" t="n">
+        <v>18</v>
       </c>
       <c r="H57" s="28" t="inlineStr">
         <is>
@@ -2890,94 +2444,906 @@
         </is>
       </c>
       <c r="P57" s="17" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E58" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O58" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P58" s="17" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" s="27" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="F59" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="G59" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P59" s="17" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="C58" s="29" t="inlineStr">
+      <c r="E60" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O60" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P60" s="17" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D61" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E61" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P61" s="17" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O62" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P62" s="17" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C63" s="27" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D63" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="G63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P63" s="17" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G64" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P64" s="17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C65" s="27" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="G65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P65" s="17" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P66" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="C67" s="27" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P67" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P68" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C69" s="27" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P69" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="D58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P58" s="17" t="n">
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P70" s="17" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
     <row r="71"/>
     <row r="72"/>
     <row r="73"/>
@@ -2989,6 +3355,18 @@
     <row r="79"/>
     <row r="80"/>
     <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
